--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193839</v>
       </c>
       <c r="B2" t="n">
-        <v>92102</v>
+        <v>92105</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193912</v>
       </c>
       <c r="B3" t="n">
-        <v>92116</v>
+        <v>92119</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193839</v>
       </c>
       <c r="B2" t="n">
-        <v>92105</v>
+        <v>92106</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193912</v>
       </c>
       <c r="B3" t="n">
-        <v>92119</v>
+        <v>92120</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193839</v>
       </c>
       <c r="B2" t="n">
-        <v>92106</v>
+        <v>92111</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193912</v>
       </c>
       <c r="B3" t="n">
-        <v>92120</v>
+        <v>92125</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -925,7 +925,7 @@
         <v>136347702</v>
       </c>
       <c r="B4" t="n">
-        <v>79474</v>
+        <v>79476</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136193839</v>
       </c>
       <c r="B2" t="n">
-        <v>92111</v>
+        <v>92113</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -804,7 +804,7 @@
         <v>136193912</v>
       </c>
       <c r="B3" t="n">
-        <v>92125</v>
+        <v>92127</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136347702</v>
       </c>
       <c r="B4" t="n">
-        <v>79476</v>
+        <v>79480</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>

--- a/artfynd/A 37166-2026 artfynd.xlsx
+++ b/artfynd/A 37166-2026 artfynd.xlsx
@@ -925,7 +925,7 @@
         <v>136347702</v>
       </c>
       <c r="B4" t="n">
-        <v>79480</v>
+        <v>79482</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
